--- a/Side Bar Files/GWD Data/Pump Pullout.xlsx
+++ b/Side Bar Files/GWD Data/Pump Pullout.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="28">
   <si>
     <t>Pump Pullout</t>
   </si>
@@ -89,7 +89,7 @@
     <t>TOTAL  </t>
   </si>
   <si>
-    <t>Borewell submersible pump pullout charges above 3 h.P. To 7.5 H.P.</t>
+    <t>Borewell submersible pump pullout charges above 3 H.P. To 7.5 H.P.</t>
   </si>
   <si>
     <t xml:space="preserve">40mm Cast iron Clamp </t>
@@ -98,31 +98,13 @@
     <t>Borewell submersible pump pullout charges above 7.5 H.P.</t>
   </si>
   <si>
-    <t>Pulling out of hand pump for repairing and re-erecting</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>Say Rs 5970 x Cost Index</t>
-  </si>
-  <si>
-    <t>Compressor pump pullout charge</t>
-  </si>
-  <si>
-    <t>Say Rs 3616 x Cost Index</t>
+    <t>Compressor pump detaching charge</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="0.000"/>
-  </numFmts>
   <fonts count="4">
     <font>
       <sz val="10"/>
@@ -131,13 +113,13 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Cambria"/>
       <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Cambria"/>
@@ -293,86 +275,100 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -758,8 +754,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A57D3675-CFBD-42D9-A0AF-38C4268FB9A6}">
-  <dimension ref="A1:F74"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B956FD55-9C3A-4FB6-90A1-DE4759E8B9A7}">
+  <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1" spans="1:6" ht="12.75">
@@ -800,223 +796,223 @@
       <c r="E3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="12.75">
-      <c r="A4" s="9"/>
-      <c r="B4" s="10" t="s">
+      <c r="A4" s="10"/>
+      <c r="B4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="12"/>
     </row>
     <row r="5" spans="1:6" ht="12.75">
-      <c r="A5" s="11"/>
-      <c r="B5" s="10" t="s">
+      <c r="A5" s="13"/>
+      <c r="B5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="12">
-        <v>0</v>
-      </c>
-      <c r="E5" s="12">
+      <c r="D5" s="14">
+        <v>0</v>
+      </c>
+      <c r="E5" s="14">
         <v>935</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="15">
         <f>D5*E5</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="12.75">
-      <c r="A6" s="11"/>
-      <c r="B6" s="14" t="s">
+      <c r="A6" s="13"/>
+      <c r="B6" s="16" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
       <c r="E6" s="7"/>
-      <c r="F6" s="13">
+      <c r="F6" s="15">
         <f>F5*0.01</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="12.75">
-      <c r="A7" s="11"/>
-      <c r="B7" s="14" t="s">
+      <c r="A7" s="13"/>
+      <c r="B7" s="16" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="7"/>
-      <c r="F7" s="13">
+      <c r="F7" s="15">
         <f>SUM(F5:F6)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="12.75">
-      <c r="A8" s="11"/>
-      <c r="B8" s="14" t="s">
+      <c r="A8" s="13"/>
+      <c r="B8" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="7"/>
-      <c r="F8" s="13">
+      <c r="F8" s="15">
         <f>F7*0.15</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="12.75">
-      <c r="A9" s="11"/>
-      <c r="B9" s="14" t="s">
+      <c r="A9" s="13"/>
+      <c r="B9" s="16" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="7"/>
-      <c r="F9" s="13">
+      <c r="F9" s="15">
         <f>SUM(F7:F8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="12.75">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="14">
         <v>0.50</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="14">
         <v>3000</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="15">
         <f>D10*E10</f>
         <v>1500</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="12.75">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="14">
         <v>1</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="14">
         <v>784</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="15">
         <f>D11*E11</f>
         <v>784</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="12.75">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="14">
         <v>1</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="14">
         <v>645</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="15">
         <f>D12*E12</f>
         <v>645</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="12.75">
-      <c r="A13" s="15"/>
-      <c r="B13" s="14" t="s">
+      <c r="A13" s="17"/>
+      <c r="B13" s="16" t="s">
         <v>23</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="7"/>
-      <c r="F13" s="13">
+      <c r="F13" s="15">
         <f>SUM(F10:F12)</f>
         <v>2929</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="12.75">
-      <c r="A14" s="15"/>
-      <c r="B14" s="14" t="s">
+      <c r="A14" s="17"/>
+      <c r="B14" s="16" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
       <c r="E14" s="7"/>
-      <c r="F14" s="13">
+      <c r="F14" s="15">
         <f>F13*0.01</f>
         <v>29.29</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="12.75">
-      <c r="A15" s="15"/>
-      <c r="B15" s="14" t="s">
+      <c r="A15" s="17"/>
+      <c r="B15" s="16" t="s">
         <v>13</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="7"/>
-      <c r="F15" s="13">
+      <c r="F15" s="15">
         <f>SUM(F13:F14)</f>
         <v>2958.29</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="12.75">
-      <c r="A16" s="15"/>
-      <c r="B16" s="14" t="s">
+      <c r="A16" s="17"/>
+      <c r="B16" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="7"/>
-      <c r="F16" s="13">
+      <c r="F16" s="15">
         <f>F15*0.15</f>
         <v>443.74349999999998</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="12.75">
-      <c r="A17" s="15"/>
-      <c r="B17" s="14" t="s">
+      <c r="A17" s="17"/>
+      <c r="B17" s="16" t="s">
         <v>13</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="7"/>
-      <c r="F17" s="13">
-        <f>SUM(F15:F16)</f>
-        <v>3402.0335</v>
+      <c r="F17" s="15">
+        <f>MROUND(SUM(F15:F16),1)</f>
+        <v>3402</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="12.75">
-      <c r="A18" s="16" t="str">
-        <f>CONCATENATE("Say Rs ",F9," + (",F17," x Cost Index)")</f>
-        <v>Say Rs 0 + (3402.0335 x Cost Index)</v>
+      <c r="A18" s="18" t="str">
+        <f>CONCATENATE("Say Rs (",F17," x Cost Index)")</f>
+        <v>Say Rs (3402 x Cost Index)</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -1025,10 +1021,10 @@
       <c r="F18" s="7"/>
     </row>
     <row r="19" spans="1:6" ht="12.75">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="20" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="6"/>
@@ -1037,238 +1033,238 @@
       <c r="F19" s="7"/>
     </row>
     <row r="20" spans="1:6" ht="12.75">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="19" t="s">
+      <c r="F20" s="22" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="12.75">
-      <c r="A21" s="20"/>
-      <c r="B21" s="21" t="s">
+      <c r="A21" s="23"/>
+      <c r="B21" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="25"/>
     </row>
     <row r="22" spans="1:6" ht="12.75">
-      <c r="A22" s="22"/>
-      <c r="B22" s="21" t="s">
+      <c r="A22" s="26"/>
+      <c r="B22" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="23">
-        <v>0</v>
-      </c>
-      <c r="E22" s="23">
+      <c r="D22" s="27">
+        <v>0</v>
+      </c>
+      <c r="E22" s="27">
         <v>935</v>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="28">
         <f>D22*E22</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="12.75">
-      <c r="A23" s="22"/>
-      <c r="B23" s="25" t="s">
+      <c r="A23" s="26"/>
+      <c r="B23" s="29" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="24">
+      <c r="F23" s="28">
         <f>F22*0.01</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="12.75">
-      <c r="A24" s="22"/>
-      <c r="B24" s="25" t="s">
+      <c r="A24" s="26"/>
+      <c r="B24" s="29" t="s">
         <v>13</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="24">
+      <c r="F24" s="28">
         <f>SUM(F22:F23)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="12.75">
-      <c r="A25" s="22"/>
-      <c r="B25" s="25" t="s">
+      <c r="A25" s="26"/>
+      <c r="B25" s="29" t="s">
         <v>14</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="24">
+      <c r="F25" s="28">
         <f>F24*0.15</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="12.75">
-      <c r="A26" s="22"/>
-      <c r="B26" s="25" t="s">
+      <c r="A26" s="26"/>
+      <c r="B26" s="29" t="s">
         <v>13</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="7"/>
-      <c r="F26" s="24">
+      <c r="F26" s="28">
         <f>SUM(F24:F25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="12.75">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="D27" s="23">
+      <c r="D27" s="27">
         <v>0.75</v>
       </c>
-      <c r="E27" s="23">
+      <c r="E27" s="27">
         <v>3000</v>
       </c>
-      <c r="F27" s="24">
+      <c r="F27" s="28">
         <f>D27*E27</f>
         <v>2250</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="12.75">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="B28" s="21" t="s">
+      <c r="B28" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="23">
+      <c r="D28" s="27">
         <v>1</v>
       </c>
-      <c r="E28" s="23">
+      <c r="E28" s="27">
         <v>784</v>
       </c>
-      <c r="F28" s="24">
+      <c r="F28" s="28">
         <f>D28*E28</f>
         <v>784</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="12.75">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="C29" s="23" t="s">
+      <c r="C29" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="23">
+      <c r="D29" s="27">
         <v>1</v>
       </c>
-      <c r="E29" s="23">
+      <c r="E29" s="27">
         <v>645</v>
       </c>
-      <c r="F29" s="24">
+      <c r="F29" s="28">
         <f>D29*E29</f>
         <v>645</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="12.75">
-      <c r="A30" s="26"/>
-      <c r="B30" s="25" t="s">
+      <c r="A30" s="30"/>
+      <c r="B30" s="29" t="s">
         <v>23</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
       <c r="E30" s="7"/>
-      <c r="F30" s="24">
+      <c r="F30" s="28">
         <f>SUM(F27:F29)</f>
         <v>3679</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="12.75">
-      <c r="A31" s="26"/>
-      <c r="B31" s="25" t="s">
+      <c r="A31" s="30"/>
+      <c r="B31" s="29" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
       <c r="E31" s="7"/>
-      <c r="F31" s="24">
+      <c r="F31" s="28">
         <f>F30*0.01</f>
         <v>36.79</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="12.75">
-      <c r="A32" s="26"/>
-      <c r="B32" s="25" t="s">
+      <c r="A32" s="30"/>
+      <c r="B32" s="29" t="s">
         <v>13</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
       <c r="E32" s="7"/>
-      <c r="F32" s="24">
+      <c r="F32" s="28">
         <f>SUM(F30:F31)</f>
         <v>3715.79</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="12.75">
-      <c r="A33" s="26"/>
-      <c r="B33" s="25" t="s">
+      <c r="A33" s="30"/>
+      <c r="B33" s="29" t="s">
         <v>14</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
       <c r="E33" s="7"/>
-      <c r="F33" s="24">
+      <c r="F33" s="28">
         <f>F32*0.15</f>
         <v>557.36850000000004</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="12.75">
-      <c r="A34" s="26"/>
-      <c r="B34" s="25" t="s">
+      <c r="A34" s="30"/>
+      <c r="B34" s="29" t="s">
         <v>13</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
       <c r="E34" s="7"/>
-      <c r="F34" s="24">
-        <f>SUM(F32:F33)</f>
-        <v>4273.1584999999995</v>
+      <c r="F34" s="28">
+        <f>MROUND(SUM(F32:F33),1)</f>
+        <v>4273</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="12.75">
-      <c r="A35" s="16" t="str">
-        <f>CONCATENATE("Say Rs ",F26," + (",F34," x Cost Index)")</f>
-        <v>Say Rs 0 + (4273.1585 x Cost Index)</v>
+      <c r="A35" s="18" t="str">
+        <f>CONCATENATE("Say Rs (",F34," x Cost Index)")</f>
+        <v>Say Rs (4273 x Cost Index)</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -1280,7 +1276,7 @@
       <c r="A36" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B36" s="27" t="s">
+      <c r="B36" s="31" t="s">
         <v>26</v>
       </c>
       <c r="C36" s="6"/>
@@ -1304,223 +1300,223 @@
       <c r="E37" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F37" s="8" t="s">
+      <c r="F37" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="12.75">
-      <c r="A38" s="9"/>
-      <c r="B38" s="10" t="s">
+      <c r="A38" s="10"/>
+      <c r="B38" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="12"/>
     </row>
     <row r="39" spans="1:6" ht="12.75">
-      <c r="A39" s="11"/>
-      <c r="B39" s="10" t="s">
+      <c r="A39" s="13"/>
+      <c r="B39" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D39" s="12">
-        <v>0</v>
-      </c>
-      <c r="E39" s="12">
+      <c r="D39" s="14">
+        <v>0</v>
+      </c>
+      <c r="E39" s="14">
         <v>935</v>
       </c>
-      <c r="F39" s="13">
+      <c r="F39" s="15">
         <f>D39*E39</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="12.75">
-      <c r="A40" s="11"/>
-      <c r="B40" s="14" t="s">
+      <c r="A40" s="13"/>
+      <c r="B40" s="16" t="s">
         <v>12</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="7"/>
-      <c r="F40" s="13">
+      <c r="F40" s="15">
         <f>F39*0.01</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="12.75">
-      <c r="A41" s="11"/>
-      <c r="B41" s="14" t="s">
+      <c r="A41" s="13"/>
+      <c r="B41" s="16" t="s">
         <v>13</v>
       </c>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
       <c r="E41" s="7"/>
-      <c r="F41" s="13">
+      <c r="F41" s="15">
         <f>SUM(F39:F40)</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="12.75">
-      <c r="A42" s="11"/>
-      <c r="B42" s="14" t="s">
+      <c r="A42" s="13"/>
+      <c r="B42" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
       <c r="E42" s="7"/>
-      <c r="F42" s="13">
+      <c r="F42" s="15">
         <f>F41*0.15</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="12.75">
-      <c r="A43" s="11"/>
-      <c r="B43" s="14" t="s">
+      <c r="A43" s="13"/>
+      <c r="B43" s="16" t="s">
         <v>13</v>
       </c>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
       <c r="E43" s="7"/>
-      <c r="F43" s="13">
+      <c r="F43" s="15">
         <f>SUM(F41:F42)</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="12.75">
-      <c r="A44" s="11" t="s">
+      <c r="A44" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C44" s="12" t="s">
+      <c r="C44" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D44" s="12">
+      <c r="D44" s="14">
         <v>1</v>
       </c>
-      <c r="E44" s="12">
+      <c r="E44" s="14">
         <v>3000</v>
       </c>
-      <c r="F44" s="13">
+      <c r="F44" s="15">
         <f>D44*E44</f>
         <v>3000</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="12.75">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="C45" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D45" s="12">
+      <c r="D45" s="14">
         <v>1</v>
       </c>
-      <c r="E45" s="12">
+      <c r="E45" s="14">
         <v>784</v>
       </c>
-      <c r="F45" s="13">
+      <c r="F45" s="15">
         <f>D45*E45</f>
         <v>784</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="12.75">
-      <c r="A46" s="11" t="s">
+      <c r="A46" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B46" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D46" s="12">
+      <c r="D46" s="14">
         <v>1</v>
       </c>
-      <c r="E46" s="12">
+      <c r="E46" s="14">
         <v>645</v>
       </c>
-      <c r="F46" s="13">
+      <c r="F46" s="15">
         <f>D46*E46</f>
         <v>645</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="12.75">
-      <c r="A47" s="15"/>
-      <c r="B47" s="14" t="s">
+      <c r="A47" s="17"/>
+      <c r="B47" s="16" t="s">
         <v>23</v>
       </c>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
       <c r="E47" s="7"/>
-      <c r="F47" s="13">
+      <c r="F47" s="15">
         <f>SUM(F44:F46)</f>
         <v>4429</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="12.75">
-      <c r="A48" s="15"/>
-      <c r="B48" s="14" t="s">
+      <c r="A48" s="17"/>
+      <c r="B48" s="16" t="s">
         <v>12</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
       <c r="E48" s="7"/>
-      <c r="F48" s="13">
+      <c r="F48" s="15">
         <f>F47*0.01</f>
         <v>44.29</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="12.75">
-      <c r="A49" s="15"/>
-      <c r="B49" s="14" t="s">
+      <c r="A49" s="17"/>
+      <c r="B49" s="16" t="s">
         <v>13</v>
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
       <c r="E49" s="7"/>
-      <c r="F49" s="13">
+      <c r="F49" s="15">
         <f>SUM(F47:F48)</f>
         <v>4473.29</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="12.75">
-      <c r="A50" s="15"/>
-      <c r="B50" s="14" t="s">
+      <c r="A50" s="17"/>
+      <c r="B50" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
       <c r="E50" s="7"/>
-      <c r="F50" s="13">
+      <c r="F50" s="15">
         <f>F49*0.15</f>
         <v>670.99350000000004</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="12.75">
-      <c r="A51" s="15"/>
-      <c r="B51" s="14" t="s">
+      <c r="A51" s="17"/>
+      <c r="B51" s="16" t="s">
         <v>13</v>
       </c>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
       <c r="E51" s="7"/>
-      <c r="F51" s="13">
-        <f>SUM(F49:F50)</f>
-        <v>5144.2834999999995</v>
+      <c r="F51" s="15">
+        <f>MROUND(SUM(F49:F50),1)</f>
+        <v>5144</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="12.75">
-      <c r="A52" s="16" t="str">
-        <f>CONCATENATE("Say Rs ",F43," + (",F51," x Cost Index)")</f>
-        <v>Say Rs 0 + (5144.2835 x Cost Index)</v>
+      <c r="A52" s="18" t="str">
+        <f>CONCATENATE("Say Rs (",F51," x Cost Index)")</f>
+        <v>Say Rs (5144 x Cost Index)</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -1529,10 +1525,10 @@
       <c r="F52" s="7"/>
     </row>
     <row r="53" spans="1:6" ht="12.75">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B53" s="27" t="s">
+      <c r="B53" s="20" t="s">
         <v>27</v>
       </c>
       <c r="C53" s="6"/>
@@ -1541,154 +1537,157 @@
       <c r="F53" s="7"/>
     </row>
     <row r="54" spans="1:6" ht="12.75">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="C54" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="D54" s="8" t="s">
+      <c r="D54" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="E54" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="F54" s="8" t="s">
+      <c r="F54" s="22" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="12.75">
-      <c r="A55" s="11"/>
-      <c r="B55" s="10" t="s">
+      <c r="A55" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="C55" s="12" t="s">
+      <c r="C55" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="D55" s="12">
-        <v>0.20</v>
-      </c>
-      <c r="E55" s="12">
+      <c r="D55" s="27">
+        <v>0.30</v>
+      </c>
+      <c r="E55" s="27">
         <v>3000</v>
       </c>
-      <c r="F55" s="13">
+      <c r="F55" s="28">
         <f>D55*E55</f>
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="12.75">
-      <c r="A56" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B56" s="10" t="s">
+      <c r="A56" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B56" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="C56" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D56" s="12">
-        <v>2.50</v>
-      </c>
-      <c r="E56" s="12">
+      <c r="D56" s="27">
+        <v>0.50</v>
+      </c>
+      <c r="E56" s="27">
         <v>784</v>
       </c>
-      <c r="F56" s="13">
+      <c r="F56" s="28">
         <f>D56*E56</f>
-        <v>1960</v>
+        <v>392</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="12.75">
-      <c r="A57" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B57" s="10" t="s">
+      <c r="A57" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B57" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="C57" s="12" t="s">
+      <c r="C57" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D57" s="12">
-        <v>4</v>
-      </c>
-      <c r="E57" s="12">
+      <c r="D57" s="27">
+        <v>0.50</v>
+      </c>
+      <c r="E57" s="27">
         <v>645</v>
       </c>
-      <c r="F57" s="13">
+      <c r="F57" s="28">
         <f>D57*E57</f>
-        <v>2580</v>
+        <v>322.50</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="12.75">
-      <c r="A58" s="15"/>
-      <c r="B58" s="14" t="s">
+      <c r="A58" s="30"/>
+      <c r="B58" s="29" t="s">
         <v>23</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="6"/>
       <c r="E58" s="7"/>
-      <c r="F58" s="13">
+      <c r="F58" s="28">
         <f>SUM(F55:F57)</f>
-        <v>5140</v>
+        <v>1614.50</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="12.75">
-      <c r="A59" s="15"/>
-      <c r="B59" s="14" t="s">
+      <c r="A59" s="30"/>
+      <c r="B59" s="29" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="6"/>
       <c r="D59" s="6"/>
       <c r="E59" s="7"/>
-      <c r="F59" s="13">
+      <c r="F59" s="28">
         <f>F58*0.01</f>
-        <v>51.40</v>
+        <v>16.145</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="12.75">
-      <c r="A60" s="15"/>
-      <c r="B60" s="14" t="s">
+      <c r="A60" s="30"/>
+      <c r="B60" s="29" t="s">
         <v>13</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="6"/>
       <c r="E60" s="7"/>
-      <c r="F60" s="13">
+      <c r="F60" s="28">
         <f>SUM(F58:F59)</f>
-        <v>5191.40</v>
+        <v>1630.645</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="12.75">
-      <c r="A61" s="15"/>
-      <c r="B61" s="14" t="s">
+      <c r="A61" s="30"/>
+      <c r="B61" s="29" t="s">
         <v>14</v>
       </c>
       <c r="C61" s="6"/>
       <c r="D61" s="6"/>
       <c r="E61" s="7"/>
-      <c r="F61" s="13">
+      <c r="F61" s="28">
         <f>F60*0.15</f>
-        <v>778.71</v>
+        <v>244.59674999999999</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="12.75">
-      <c r="A62" s="15"/>
-      <c r="B62" s="14" t="s">
+      <c r="A62" s="30"/>
+      <c r="B62" s="29" t="s">
         <v>13</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="6"/>
       <c r="E62" s="7"/>
-      <c r="F62" s="13">
-        <f>SUM(F60:F61)</f>
-        <v>5970.11</v>
+      <c r="F62" s="28">
+        <f>MROUND(SUM(F60:F61),1)</f>
+        <v>1875</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="12.75">
-      <c r="A63" s="16" t="s">
-        <v>30</v>
+      <c r="A63" s="18" t="str">
+        <f>CONCATENATE("Say Rs (",F62," x Cost Index)")</f>
+        <v>Say Rs (1875 x Cost Index)</v>
       </c>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -1696,178 +1695,8 @@
       <c r="E63" s="6"/>
       <c r="F63" s="7"/>
     </row>
-    <row r="64" spans="1:6" ht="12.75">
-      <c r="A64" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B64" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="6"/>
-      <c r="F64" s="7"/>
-    </row>
-    <row r="65" spans="1:6" ht="12.75">
-      <c r="A65" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="B65" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D65" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E65" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F65" s="19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="12.75">
-      <c r="A66" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="D66" s="23">
-        <v>0.30</v>
-      </c>
-      <c r="E66" s="23">
-        <v>3000</v>
-      </c>
-      <c r="F66" s="24">
-        <f>D66*E66</f>
-        <v>900</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="12.75">
-      <c r="A67" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="B67" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="C67" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="D67" s="23">
-        <v>0.50</v>
-      </c>
-      <c r="E67" s="23">
-        <v>784</v>
-      </c>
-      <c r="F67" s="24">
-        <f>D67*E67</f>
-        <v>392</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="12.75">
-      <c r="A68" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B68" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C68" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="D68" s="23">
-        <v>0.50</v>
-      </c>
-      <c r="E68" s="23">
-        <v>645</v>
-      </c>
-      <c r="F68" s="24">
-        <f>D68*E68</f>
-        <v>322.50</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="12.75">
-      <c r="A69" s="26"/>
-      <c r="B69" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="24">
-        <f>SUM(F66:F68)</f>
-        <v>1614.50</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="12.75">
-      <c r="A70" s="26"/>
-      <c r="B70" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="C70" s="6"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="24">
-        <f>F69*0.01</f>
-        <v>16.145</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="12.75">
-      <c r="A71" s="26"/>
-      <c r="B71" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C71" s="6"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="24">
-        <f>SUM(F69:F70)</f>
-        <v>1630.645</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="12.75">
-      <c r="A72" s="26"/>
-      <c r="B72" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="C72" s="6"/>
-      <c r="D72" s="6"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="24">
-        <f>F71*0.15</f>
-        <v>244.59674999999999</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="12.75">
-      <c r="A73" s="26"/>
-      <c r="B73" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="28">
-        <f>SUM(F71:F72)</f>
-        <v>1875.2417499999999</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="12.75">
-      <c r="A74" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="6"/>
-      <c r="F74" s="7"/>
-    </row>
   </sheetData>
-  <mergeCells count="48">
+  <mergeCells count="41">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B6:E6"/>
@@ -1896,6 +1725,12 @@
     <mergeCell ref="B41:E41"/>
     <mergeCell ref="B42:E42"/>
     <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="A63:F63"/>
     <mergeCell ref="B47:E47"/>
     <mergeCell ref="B48:E48"/>
     <mergeCell ref="B49:E49"/>
@@ -1903,19 +1738,6 @@
     <mergeCell ref="B51:E51"/>
     <mergeCell ref="A52:F52"/>
     <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="B71:E71"/>
-    <mergeCell ref="B72:E72"/>
-    <mergeCell ref="B73:E73"/>
-    <mergeCell ref="A74:F74"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="B62:E62"/>
-    <mergeCell ref="A63:F63"/>
-    <mergeCell ref="B64:F64"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Side Bar Files/GWD Data/Pump Pullout.xlsx
+++ b/Side Bar Files/GWD Data/Pump Pullout.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="28">
   <si>
     <t>Pump Pullout</t>
   </si>
@@ -250,25 +250,11 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -373,11 +359,11 @@
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -754,7 +740,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B956FD55-9C3A-4FB6-90A1-DE4759E8B9A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3566061B-BD11-4C42-B8CA-6534163BBAA6}">
   <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
@@ -811,7 +797,9 @@
       <c r="F4" s="12"/>
     </row>
     <row r="5" spans="1:6" ht="12.75">
-      <c r="A5" s="13"/>
+      <c r="A5" s="13" t="s">
+        <v>1</v>
+      </c>
       <c r="B5" s="11" t="s">
         <v>10</v>
       </c>
@@ -1063,7 +1051,9 @@
       <c r="F21" s="25"/>
     </row>
     <row r="22" spans="1:6" ht="12.75">
-      <c r="A22" s="26"/>
+      <c r="A22" s="26" t="s">
+        <v>1</v>
+      </c>
       <c r="B22" s="24" t="s">
         <v>25</v>
       </c>
@@ -1315,7 +1305,9 @@
       <c r="F38" s="12"/>
     </row>
     <row r="39" spans="1:6" ht="12.75">
-      <c r="A39" s="13"/>
+      <c r="A39" s="13" t="s">
+        <v>1</v>
+      </c>
       <c r="B39" s="11" t="s">
         <v>25</v>
       </c>

--- a/Side Bar Files/GWD Data/Pump Pullout.xlsx
+++ b/Side Bar Files/GWD Data/Pump Pullout.xlsx
@@ -740,7 +740,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3566061B-BD11-4C42-B8CA-6534163BBAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEE2E766-6505-41AF-8F9A-509646D9BAA6}">
   <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/Pump Pullout.xlsx
+++ b/Side Bar Files/GWD Data/Pump Pullout.xlsx
@@ -740,7 +740,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEE2E766-6505-41AF-8F9A-509646D9BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C92A24CC-D50D-4E96-9581-7C79D495BAA6}">
   <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
